--- a/data/employees/EMP083/AST-EMP083-06.xlsx
+++ b/data/employees/EMP083/AST-EMP083-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Resource Utilization" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>System Resource Utilization - Taylor Miller (IT)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Taylor Miller | Role: Lead | Location: Austin | Date: 2025-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>93</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Server</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>CPU %</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Memory %</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Disk %</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Network (Mbps)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>65</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PROD-APP-01</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>42</v>
-      </c>
-      <c r="C5" t="n">
-        <v>67</v>
-      </c>
-      <c r="D5" t="n">
-        <v>55</v>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>1200</v>
+        <v>90</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Automation backlog refinement. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PROD-SQL-02</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>58</v>
-      </c>
-      <c r="C6" t="n">
-        <v>81</v>
-      </c>
-      <c r="D6" t="n">
-        <v>88</v>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>880</v>
+        <v>85</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>Section 1: Department KPI performance. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DEV-WEB-01</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>15</v>
-      </c>
-      <c r="C7" t="n">
-        <v>34</v>
-      </c>
-      <c r="D7" t="n">
-        <v>40</v>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>200</v>
+        <v>72</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Fabric semantic model planning. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TEST-API-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>28</v>
-      </c>
-      <c r="C8" t="n">
-        <v>52</v>
-      </c>
-      <c r="D8" t="n">
-        <v>62</v>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>450</v>
+        <v>95</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Customer escalation analysis. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>77</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>76</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>83</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>93</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>77</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>91</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>84</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>89</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>61</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>95</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>91</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>73</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>67</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>97</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>97</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>78</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp083 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>79</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP083</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP083 contributes to ast emp083 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>